--- a/Data/collapsed database manual cases/veracruz_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/veracruz_collapsed_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB0488B-ADAE-F941-9465-00046AAA42EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B640E0-0A39-944E-90D6-6B47039C7A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$1106</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13048" uniqueCount="2965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13585" uniqueCount="3146">
   <si>
     <t>uniqueid</t>
   </si>
@@ -8918,6 +8931,549 @@
   </si>
   <si>
     <t>JUANA MARIA MARTINEZ GUERRERO</t>
+  </si>
+  <si>
+    <t>JUAN IGNACIO VLADIMIR MORALES GUEVARA</t>
+  </si>
+  <si>
+    <t>PODEMOS</t>
+  </si>
+  <si>
+    <t>GUSTAVO FLORES COLORADO</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO VENTURA DE LA PAZ</t>
+  </si>
+  <si>
+    <t>MARIO ALBERTO VARGAS AMADOR</t>
+  </si>
+  <si>
+    <t>CARLOS GARCIA DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL DE UNANUE ABASCAL</t>
+  </si>
+  <si>
+    <t>UC</t>
+  </si>
+  <si>
+    <t>CIRILO DOROTEO ESTEBAN</t>
+  </si>
+  <si>
+    <t>JOSE RODOLFO DURAN MENDEZ</t>
+  </si>
+  <si>
+    <t>GABRIELA ALEJANDRA ORTEGA MOLINA</t>
+  </si>
+  <si>
+    <t>JOSE LUIS ALONSO JUAREZ</t>
+  </si>
+  <si>
+    <t>JOSE SATURNINO BELTRAN VASQUEZ</t>
+  </si>
+  <si>
+    <t>JUAN PABLO GOMEZ MENDOZA</t>
+  </si>
+  <si>
+    <t>MARTIN RICO MARTINEZ</t>
+  </si>
+  <si>
+    <t>GABRIEL MORELOS FRANCISCO</t>
+  </si>
+  <si>
+    <t>NESTOR ENRIQUE SOSA PEÑA</t>
+  </si>
+  <si>
+    <t>PAULINO ROBERTO SALINAS SALGADO</t>
+  </si>
+  <si>
+    <t>MIGUEL JERONIMO VEGA</t>
+  </si>
+  <si>
+    <t>PES</t>
+  </si>
+  <si>
+    <t>JAVIER VALLADARES AGUSTIN</t>
+  </si>
+  <si>
+    <t>TXVER</t>
+  </si>
+  <si>
+    <t>ANDRES CHACON HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MORENA</t>
+  </si>
+  <si>
+    <t>https://lasillarota.com/veracruz/reportajes/2024/1/28/cuantos-votos-sumaran-alcaldes-que-brincaron-morena-para-apoyar-rocio-nahle-467246.html</t>
+  </si>
+  <si>
+    <t>EFRAIN PEREZ CRUZ</t>
+  </si>
+  <si>
+    <t>FORTUNATO RUIZ VARGAS</t>
+  </si>
+  <si>
+    <t>RAUL ANDRADE GONZALEZ</t>
+  </si>
+  <si>
+    <t>AUGUSTO NAHUM ALVAREZ PELLICO</t>
+  </si>
+  <si>
+    <t>DAVID MEZA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BALBINO CASTILLO MURRIETA</t>
+  </si>
+  <si>
+    <t>ERIC RODRIGUEZ BARCENAS</t>
+  </si>
+  <si>
+    <t>PABLO DOMINGUEZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>BONIFACIO ANTONIO SOSA</t>
+  </si>
+  <si>
+    <t>MIGUEL VERJEL VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CARDENISTA</t>
+  </si>
+  <si>
+    <t>JAIRO CESAR MARTINEZ GONZALEZ</t>
+  </si>
+  <si>
+    <t>PFCRN</t>
+  </si>
+  <si>
+    <t>AGUSTIN RAMOS HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RUTH GARCIA MEZA</t>
+  </si>
+  <si>
+    <t>JOSE DE JESUS LANDA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MANUEL DIONICIO ROJAS MONTANE</t>
+  </si>
+  <si>
+    <t>ARMANDO ALVAREZ MORALES</t>
+  </si>
+  <si>
+    <t>DEMETRIO CRUZ DE JESUS</t>
+  </si>
+  <si>
+    <t>CELERINO HERNANDEZ MENA</t>
+  </si>
+  <si>
+    <t>NESTOR RODOLFO RIVERA PEREZ</t>
+  </si>
+  <si>
+    <t>JIMMY JONATHAN ZUÑIGA RINCON</t>
+  </si>
+  <si>
+    <t>JOSE LUIS FLORES SUBIAUR</t>
+  </si>
+  <si>
+    <t>https://avcnoticias.com.mx/columna.php?id=19952&amp;idc=133#google_vignette</t>
+  </si>
+  <si>
+    <t>CLAUDIA ROSALES COLINA</t>
+  </si>
+  <si>
+    <t>CARLOS GARCIA MORENO</t>
+  </si>
+  <si>
+    <t>OTILIO SALAS CERVANTES</t>
+  </si>
+  <si>
+    <t>GILDARDO APODACA QUIÑONES</t>
+  </si>
+  <si>
+    <t>EDER JERO HERNANDEZ LARA</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://www.masnoticias.mx/alcalde-de-ursulo-galvan-se-suma-al-proyecto-de-rocio-nahle-ramirez-zepeta/&amp;ved=2ahUKEwjuuvjywPeSAxVnI0QIHZqbN3sQFnoECDAQAQ&amp;usg=AOvVaw0930TibQo_yDHXEhVFnSKF</t>
+  </si>
+  <si>
+    <t>MILEN CUEVAS DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GUADALUPE ROMERO SANCHEZ</t>
+  </si>
+  <si>
+    <t>FERNANDO NICOLAS GORDILLO TORRES</t>
+  </si>
+  <si>
+    <t>FERNANDO LUNA SOLIS</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL DE LA GARZA SANCHEZ</t>
+  </si>
+  <si>
+    <t>ONAN HERNANDEZ LOPEZ</t>
+  </si>
+  <si>
+    <t>ALONSO JAIMES AYALA</t>
+  </si>
+  <si>
+    <t>https://lasillarota.com/veracruz/estado/2021/2/22/16-municipes-del-panal-se-van-con-morena-en-pleno-proceso-electoral-268614.html</t>
+  </si>
+  <si>
+    <t>ANSBERTO MARINO ESPINOZA MURILLO</t>
+  </si>
+  <si>
+    <t>PAN_PRI_PRD</t>
+  </si>
+  <si>
+    <t>ROSALBA RODRIGUEZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PVEM_PT_MORENA</t>
+  </si>
+  <si>
+    <t>ROCIO CRUZ DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>URIEL GONZALEZ ALARCON</t>
+  </si>
+  <si>
+    <t>LUIS VICENTE AGUILAR CASTILLO</t>
+  </si>
+  <si>
+    <t>LIZZETTE ALVAREZ VERA</t>
+  </si>
+  <si>
+    <t>PT_MORENA</t>
+  </si>
+  <si>
+    <t>ALMA ROSA CLARA RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUIS ARTURO FIGUEROA VARGAS</t>
+  </si>
+  <si>
+    <t>CRESCENCIA TZOMPAXTLE ITEHUA</t>
+  </si>
+  <si>
+    <t>DAVID SANGABRIEL BONILLA</t>
+  </si>
+  <si>
+    <t>GUADALUPE ROSAS CARRILLO</t>
+  </si>
+  <si>
+    <t>HECTOR RODRIGUEZ CORTES</t>
+  </si>
+  <si>
+    <t>RAYMUNDO ANDRADE RIVERA</t>
+  </si>
+  <si>
+    <t>AMADO JESUS CRUZ MALPICA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GARCIA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JUAN MARTINEZ FLORES</t>
+  </si>
+  <si>
+    <t>BERTHA ISABEL MU√ëOZ TORRES</t>
+  </si>
+  <si>
+    <t>LUIS SILVESTRE MORALES VIVEROS</t>
+  </si>
+  <si>
+    <t>ARMANDO FERNANDEZ DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>RAMIRO ALEMAN VALENCIA</t>
+  </si>
+  <si>
+    <t>MARIELA HERNANDEZ GARCIA</t>
+  </si>
+  <si>
+    <t>ERICK RUIZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GERARDO ROSALES VICTORIA</t>
+  </si>
+  <si>
+    <t>FRANS APARICIO REYES</t>
+  </si>
+  <si>
+    <t>VENTURA DEMUNER TORRES</t>
+  </si>
+  <si>
+    <t>MANUEL LEMUS SALAZAR</t>
+  </si>
+  <si>
+    <t>JUAN GOMEZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>LIZETH MENDEZ ROSAS</t>
+  </si>
+  <si>
+    <t>DORA ANGELICA GALICIA CONTRERAS</t>
+  </si>
+  <si>
+    <t>FERNANDO OCHOA VERGARA</t>
+  </si>
+  <si>
+    <t>FABIAN DE JESUS CRUZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JESUS MIGUEL PEREZ TOTO</t>
+  </si>
+  <si>
+    <t>LUIS YOVAL MALDONADO</t>
+  </si>
+  <si>
+    <t>CRUZ ULISES CUEVAS HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE DURAN ALCANTARA</t>
+  </si>
+  <si>
+    <t>RODRIGO CALDERON SALAS</t>
+  </si>
+  <si>
+    <t>ANTONIO CERVANTES VARGAS</t>
+  </si>
+  <si>
+    <t>MARCOS ISLE√ëO ANDRADE</t>
+  </si>
+  <si>
+    <t>CARMEN MEDEL PALMA</t>
+  </si>
+  <si>
+    <t>NORMA ESTELA HERNANDEZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>LUIS MANUEL MONTERO HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ALEIDA TEPEPA MARQUEZ</t>
+  </si>
+  <si>
+    <t>ERNESTO TORRES NAVARRO</t>
+  </si>
+  <si>
+    <t>OLGA JARED MANZANILLA MEDINA</t>
+  </si>
+  <si>
+    <t>OSCAR GUZMAN DE PAZ</t>
+  </si>
+  <si>
+    <t>ERIC DOMINGUEZ VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BLANCA ESTELA HERNANDEZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MARIO MAFARA RAMIREZ</t>
+  </si>
+  <si>
+    <t>DELFINO ORTEGA MARTINEZ</t>
+  </si>
+  <si>
+    <t>GUILEBALDO FLORES LOPEZ</t>
+  </si>
+  <si>
+    <t>URBANO BAUTISTA MARTINEZ</t>
+  </si>
+  <si>
+    <t>FERNANDO LUIS REMES GARZA</t>
+  </si>
+  <si>
+    <t>VALERIA NIETO REYNOSO</t>
+  </si>
+  <si>
+    <t>ROBERTO MONTIEL MONTIEL</t>
+  </si>
+  <si>
+    <t>RICARDO PEREZ GARCIA</t>
+  </si>
+  <si>
+    <t>MARIA ELENA SOLANA CALZADA</t>
+  </si>
+  <si>
+    <t>JUSTINO GUILLEN LAGUNES</t>
+  </si>
+  <si>
+    <t>BRIANDA KRISTEL HERNANDEZ TOPETE</t>
+  </si>
+  <si>
+    <t>ELIZABETH REYES MORALES</t>
+  </si>
+  <si>
+    <t>ARANTXA LIZBETH ZAMITIZ SOSA</t>
+  </si>
+  <si>
+    <t>RAFAEL HERNANDEZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROSALIA MU√ëOZ MENDO</t>
+  </si>
+  <si>
+    <t>MARIA LUISA SALAZAR MARIN</t>
+  </si>
+  <si>
+    <t>GABRIELA VALDEZ SANTES</t>
+  </si>
+  <si>
+    <t>BLANCA LILIA ARRIETA PARDO</t>
+  </si>
+  <si>
+    <t>LEONARDO DANIEL AGUILAR HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GIOVANNY AULI MOO</t>
+  </si>
+  <si>
+    <t>MARIA REGINA CALIXTO TELLO</t>
+  </si>
+  <si>
+    <t>ALVARO GOMEZ FLORES</t>
+  </si>
+  <si>
+    <t>NANCY RUEDA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SALVADOR MURRIETA MORENO</t>
+  </si>
+  <si>
+    <t>NORA MARIA ACOSTA GAMBOA</t>
+  </si>
+  <si>
+    <t>LEIDY DEL CARMEN VERGARA ANDRADE</t>
+  </si>
+  <si>
+    <t>PATRICIA LOBEIRA RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BENITO AGUAS ATLAHUA</t>
+  </si>
+  <si>
+    <t>SERAFIN PEREZ CARMONA</t>
+  </si>
+  <si>
+    <t>JOSE NOE CASTILLO OLVERA</t>
+  </si>
+  <si>
+    <t>ESMERALDA MORA ZAMUDIO</t>
+  </si>
+  <si>
+    <t>MARIA ISELA LOPEZ ALVAREZ</t>
+  </si>
+  <si>
+    <t>JL</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/p/1bDdpT6dHE/</t>
+  </si>
+  <si>
+    <t>https://alcalorpolitico.com/informacion/columnas.php?idcolumna=19544&amp;c=2</t>
+  </si>
+  <si>
+    <t>Pedro Luis Vergara Galo</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/p/Crescencia-Tzompaxtle-Itehua-100067455774953/</t>
+  </si>
+  <si>
+    <t>https://semmexico-mx.translate.goog/a-balazos-privan-de-la-vida-a-esposo-de-la-alcaldesa-de-calcahualco-veracruz/?_x_tr_sl=es&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=sc</t>
+  </si>
+  <si>
+    <t>https://lasillarota.com/veracruz/reportajes/2025/4/20/cirilo-ponciano-vazquez-dos-hermanos-intercambiando-la-alcaldia-en-cosoleacaque-los-ultimos-15-anos-532575.html</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/PartidoVerdeVer/posts/representando-al-pvem-en-veracruz-y-a-la-secretaria-general-del-partido-verde-en/6671733279567703/</t>
+  </si>
+  <si>
+    <t>https://x.com/Frans_Aparicio</t>
+  </si>
+  <si>
+    <t>https://www.milenio.com/politica/elecciones-2021/veracruz-candidato-morena-denuncia-ataque-armado</t>
+  </si>
+  <si>
+    <t>https://oem.com.mx/diariodexalapa/local/morena-define-candidatos-a-las-presidencias-municipales-del-estado-la-comision-nacional-de-elecciones-de-morena-dio-a-conocer-a-sus-candidatos-15541175</t>
+  </si>
+  <si>
+    <t>https://www.elbuentono.com.mx/dora-galicia-traiciona-a-morena-y-protege-a-su-circulo-de-corrupcion-en-ixhuatlan-del-cafe/</t>
+  </si>
+  <si>
+    <t>https://www.noticieroparentesis.tv/2021/04/28/prd-define-candidato-a-la-alcaldia-de-ixhuatlancillo/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/reel/1447659833039127</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://diariodelistmo.com/estatal/alcalde-de-jaltipan-concluira-su-mandato-bajo-custodia-de-la-guardia-nacional-20251213-0045.html&amp;ved=2ahUKEwjMx5Xoq7eTAxXyJUQIHdIIIuUQFnoECCkQAQ&amp;usg=AOvVaw2_raVRrUTD_TRLnueECYOn</t>
+  </si>
+  <si>
+    <t>https://enlaceveracruz212.com.mx/nota.php?id=88690</t>
+  </si>
+  <si>
+    <t>https://oem.com.mx/diariodexalapa/local/nepotismo-en-veracruz-lista-de-casos-detectados-en-la-proxima-eleccion-estatal-2025-21578697</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://www.gobernantes.com/vernota.php%3Fid%3D501521&amp;ved=2ahUKEwiArOnirLeTAxVih-4BHaxeM2kQFnoECB0QAQ&amp;usg=AOvVaw02iezsnGg4yQnvwHtNglCu</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LaLibreExpresion2021/posts/con-amenazas-jared-manzanilla-cambia-a-la-candidata-del-pvem-morena-en-otatitlán/1226968025466386/</t>
+  </si>
+  <si>
+    <t>https://lasillarota.com/veracruz/reportajes/2024/3/17/los-ramirez-un-cacicazgo-con-historial-sangriento-que-silencio-al-priismo-veracruzano-474414.html</t>
+  </si>
+  <si>
+    <t>https://imagendeveracruz.mx/estado/quien-es-guilebaldo-flores-lopez-el-nuevo-director-de-espacios-educativos-en-veracruz-20260108-0073.html</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/reportajeveracruzano/photos/pozarica-nepotismo-en-morena-pulpo-remes-desafía-el-discurso-anticorrupción-de-c/624915836764624/?_rdr</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://repositoriodocumental.ine.mx/xmlui/bitstream/handle/123456789/144174/cvopl-4so-2018-12-11-p8-anexo7.xlsx&amp;ved=2ahUKEwjPwsz-rbeTAxUPHUQIHXmlGI4QFnoECBwQAQ&amp;usg=AOvVaw3FQBTIKMXUx92SiHQK8X1Q</t>
+  </si>
+  <si>
+    <t>https://semanarionoticias.com/2021/05/temo-baruch-candidato-de-morena-a-la-alcaldia-de-soconusco-con-paso-firme-rumbo-a-la-victoria/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;url=https%3A%2F%2Fwww.facebook.com%2FMarceloRuizMX%2Fphotos%2Fa.1010868082375055%2F4490614131067082%2F%3Ftype%3D3&amp;ved=0CBYQjRxqFwoTCPD8xKaut5MDFQAAAAAdAAAAABAH&amp;opi=89978449</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;url=https%3A%2F%2Fwww.facebook.com%2FSOLEDADEDOBLADO%2Fposts%2Fingeniera-shole%25C3%25B1a-se-punta-para-la-candidatura-a-alcald%25C3%25ADa-en-soledad-de-doblado-%2F4014260038613913%2F&amp;ved=0CBoQjhxqFwoTCJC2xbGut5MDFQAAAAAdAAAAABAH&amp;opi=89978449</t>
+  </si>
+  <si>
+    <t>https://avcnoticias.com.mx/reportaje-especial-veracruz/especiales-avc/351267/una-veintena-de-pol-ticos-chapulines-que-brincaron-a-otro-partido.html</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/SRTOficial/posts/de-tantima-la-ciudadana-rosalia-muñoz-mendo-la-lic-rosalia-álvarez-muñoz-congres/1399496327967674/</t>
+  </si>
+  <si>
+    <t>https://www.sdpnoticias.com/estados/veracruz/quien-es-lilia-arrieta-la-alcaldesa-de-alamo-veracruz/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/estebanramirezzepeta/posts/por-la-mañana-recibimos-a-los-alcaldes-de-tepetlán-leonardo-daniel-aguilar-herna/1206556224803758/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Ing.Giovanny.Auli/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=http://www.pvemveracruz.org/transparencia/curriculums/NORAMARIAACOSTAGAMBOA.pdf&amp;ved=2ahUKEwiozvyar7eTAxU7le4BHYErJWMQFnoECB0QAQ&amp;usg=AOvVaw3Tvtv0htnLlpYvWZAEBL35</t>
+  </si>
+  <si>
+    <t>https://plumaslibres.com.mx/2025/10/21/alcaldesa-morenista-de-tuxtilla-leidy-del-carmen-vergara-viaja-por-el-mundo-y-suspende-servicios-en-el-ayuntamiento/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://www.jornada.com.mx/notas/2021/12/30/estados/confirman-triunfo-de-panista-patricia-lobeira-en-alcaldia-de-veracruz/&amp;ved=2ahUKEwjGzdm8r7eTAxVehe4BHcjvK-sQFnoECBcQAQ&amp;usg=AOvVaw2dw3x_QNUPHa2EUna0dcuP</t>
+  </si>
+  <si>
+    <t>https://www.eluniversal.com.mx/articulo/estados/2016/04/23/repudia-pan-atentado-contra-edil-en-veracruz/#:~:text=%22El%20atentado%20contra%20el%20Presidente%20Municipal%20de,Partido%20Acción%20Nacional%20exige%20que%20se%20investigue</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/PANVeracruz2018/posts/pan-condena-ataque-contra-alcaldesa-de-santiago-sochiapan-maría-isela-lópez-álva/1314194143396343/</t>
   </si>
 </sst>
 </file>
@@ -8967,12 +9523,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9278,7 +9835,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S1117"/>
+  <dimension ref="A1:S1267"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -9289,7 +9846,7 @@
     <col min="6" max="6" width="44.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="255.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.5" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="39.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -62458,6 +63015,2817 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1118" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1118">
+        <v>30008</v>
+      </c>
+      <c r="B1118">
+        <v>2025</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1118" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1119">
+        <v>30010</v>
+      </c>
+      <c r="B1119">
+        <v>2025</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>2965</v>
+      </c>
+      <c r="H1119" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1120">
+        <v>30017</v>
+      </c>
+      <c r="B1120">
+        <v>2025</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>2967</v>
+      </c>
+      <c r="H1120" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1121">
+        <v>30021</v>
+      </c>
+      <c r="B1121">
+        <v>2025</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>2968</v>
+      </c>
+      <c r="H1121" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1122">
+        <v>30022</v>
+      </c>
+      <c r="B1122">
+        <v>2025</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>2969</v>
+      </c>
+      <c r="H1122" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1123">
+        <v>30023</v>
+      </c>
+      <c r="B1123">
+        <v>2025</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>2970</v>
+      </c>
+      <c r="H1123" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1124">
+        <v>30028</v>
+      </c>
+      <c r="B1124">
+        <v>2025</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>2971</v>
+      </c>
+      <c r="H1124" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1125">
+        <v>30035</v>
+      </c>
+      <c r="B1125">
+        <v>2025</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>2972</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>2973</v>
+      </c>
+      <c r="H1125" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1126">
+        <v>30036</v>
+      </c>
+      <c r="B1126">
+        <v>2025</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F1126" t="s">
+        <v>2974</v>
+      </c>
+      <c r="H1126" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1127">
+        <v>30042</v>
+      </c>
+      <c r="B1127">
+        <v>2025</v>
+      </c>
+      <c r="E1127" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1127" t="s">
+        <v>2975</v>
+      </c>
+      <c r="H1127" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1128">
+        <v>30047</v>
+      </c>
+      <c r="B1128">
+        <v>2025</v>
+      </c>
+      <c r="E1128" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1128" t="s">
+        <v>2976</v>
+      </c>
+      <c r="H1128" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1129">
+        <v>30049</v>
+      </c>
+      <c r="B1129">
+        <v>2025</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>2977</v>
+      </c>
+      <c r="H1129" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1130">
+        <v>30050</v>
+      </c>
+      <c r="B1130">
+        <v>2025</v>
+      </c>
+      <c r="E1130" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1130" t="s">
+        <v>2978</v>
+      </c>
+      <c r="H1130" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1131">
+        <v>30052</v>
+      </c>
+      <c r="B1131">
+        <v>2025</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>765</v>
+      </c>
+      <c r="H1131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1132">
+        <v>30053</v>
+      </c>
+      <c r="B1132">
+        <v>2025</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>2979</v>
+      </c>
+      <c r="H1132" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1133">
+        <v>30055</v>
+      </c>
+      <c r="B1133">
+        <v>2025</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1133" t="s">
+        <v>803</v>
+      </c>
+      <c r="H1133" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1134">
+        <v>30056</v>
+      </c>
+      <c r="B1134">
+        <v>2025</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>824</v>
+      </c>
+      <c r="H1134" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1135">
+        <v>30060</v>
+      </c>
+      <c r="B1135">
+        <v>2025</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>2980</v>
+      </c>
+      <c r="H1135" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1136">
+        <v>30063</v>
+      </c>
+      <c r="B1136">
+        <v>2025</v>
+      </c>
+      <c r="E1136" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>2981</v>
+      </c>
+      <c r="H1136" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1137">
+        <v>30066</v>
+      </c>
+      <c r="B1137">
+        <v>2025</v>
+      </c>
+      <c r="E1137" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>2982</v>
+      </c>
+      <c r="H1137" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1138">
+        <v>30067</v>
+      </c>
+      <c r="B1138">
+        <v>2025</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>2983</v>
+      </c>
+      <c r="H1138" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1139">
+        <v>30070</v>
+      </c>
+      <c r="B1139">
+        <v>2025</v>
+      </c>
+      <c r="E1139" t="s">
+        <v>2984</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>2985</v>
+      </c>
+      <c r="H1139" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1140">
+        <v>30075</v>
+      </c>
+      <c r="B1140">
+        <v>2025</v>
+      </c>
+      <c r="E1140" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>2987</v>
+      </c>
+      <c r="H1140" t="s">
+        <v>2986</v>
+      </c>
+      <c r="I1140" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1141">
+        <v>30078</v>
+      </c>
+      <c r="B1141">
+        <v>2025</v>
+      </c>
+      <c r="E1141" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>2990</v>
+      </c>
+      <c r="H1141" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1142">
+        <v>30079</v>
+      </c>
+      <c r="B1142">
+        <v>2025</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>2991</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1143">
+        <v>30084</v>
+      </c>
+      <c r="B1143">
+        <v>2025</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>2972</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>2992</v>
+      </c>
+      <c r="H1143" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1144">
+        <v>30085</v>
+      </c>
+      <c r="B1144">
+        <v>2025</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>2988</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>2993</v>
+      </c>
+      <c r="H1144" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1145">
+        <v>30088</v>
+      </c>
+      <c r="B1145">
+        <v>2025</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>2994</v>
+      </c>
+      <c r="H1145" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1146">
+        <v>30090</v>
+      </c>
+      <c r="B1146">
+        <v>2025</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>2972</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H1146" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1147">
+        <v>30093</v>
+      </c>
+      <c r="B1147">
+        <v>2025</v>
+      </c>
+      <c r="E1147" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>2995</v>
+      </c>
+      <c r="H1147" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1148">
+        <v>30094</v>
+      </c>
+      <c r="B1148">
+        <v>2025</v>
+      </c>
+      <c r="E1148" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>2996</v>
+      </c>
+      <c r="H1148" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1149">
+        <v>30096</v>
+      </c>
+      <c r="B1149">
+        <v>2025</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>2997</v>
+      </c>
+      <c r="H1149" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1150">
+        <v>30103</v>
+      </c>
+      <c r="B1150">
+        <v>2025</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>2998</v>
+      </c>
+      <c r="H1150" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1151">
+        <v>30114</v>
+      </c>
+      <c r="B1151">
+        <v>2025</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>2999</v>
+      </c>
+      <c r="H1151" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1152">
+        <v>30120</v>
+      </c>
+      <c r="B1152">
+        <v>2025</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>3000</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>3001</v>
+      </c>
+      <c r="H1152" t="s">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1153">
+        <v>30121</v>
+      </c>
+      <c r="B1153">
+        <v>2025</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>3003</v>
+      </c>
+      <c r="H1153" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1154">
+        <v>30127</v>
+      </c>
+      <c r="B1154">
+        <v>2025</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>3004</v>
+      </c>
+      <c r="H1154" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1155">
+        <v>30132</v>
+      </c>
+      <c r="B1155">
+        <v>2025</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>2972</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>3005</v>
+      </c>
+      <c r="H1155" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1156">
+        <v>30139</v>
+      </c>
+      <c r="B1156">
+        <v>2025</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>3006</v>
+      </c>
+      <c r="H1156" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1157">
+        <v>30140</v>
+      </c>
+      <c r="B1157">
+        <v>2025</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>3007</v>
+      </c>
+      <c r="H1157" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1158">
+        <v>30147</v>
+      </c>
+      <c r="B1158">
+        <v>2025</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>3008</v>
+      </c>
+      <c r="H1158" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1159">
+        <v>30153</v>
+      </c>
+      <c r="B1159">
+        <v>2025</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>3009</v>
+      </c>
+      <c r="H1159" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1160">
+        <v>30155</v>
+      </c>
+      <c r="B1160">
+        <v>2025</v>
+      </c>
+      <c r="E1160" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H1160" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1161">
+        <v>30161</v>
+      </c>
+      <c r="B1161">
+        <v>2025</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>2984</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>3010</v>
+      </c>
+      <c r="H1161" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1162">
+        <v>30163</v>
+      </c>
+      <c r="B1162">
+        <v>2025</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>2263</v>
+      </c>
+      <c r="H1162" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1163">
+        <v>30165</v>
+      </c>
+      <c r="B1163">
+        <v>2025</v>
+      </c>
+      <c r="E1163" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>3011</v>
+      </c>
+      <c r="H1163" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1164">
+        <v>30167</v>
+      </c>
+      <c r="B1164">
+        <v>2025</v>
+      </c>
+      <c r="E1164" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1164" t="s">
+        <v>2324</v>
+      </c>
+      <c r="H1164" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1165">
+        <v>30172</v>
+      </c>
+      <c r="B1165">
+        <v>2025</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>3012</v>
+      </c>
+      <c r="H1165" t="s">
+        <v>2986</v>
+      </c>
+      <c r="I1165" t="s">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1166">
+        <v>30173</v>
+      </c>
+      <c r="B1166">
+        <v>2025</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1166" t="s">
+        <v>3014</v>
+      </c>
+      <c r="H1166" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1167">
+        <v>30179</v>
+      </c>
+      <c r="B1167">
+        <v>2022</v>
+      </c>
+      <c r="H1167" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1167" t="s">
+        <v>3027</v>
+      </c>
+      <c r="K1167" t="s">
+        <v>3028</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1168">
+        <v>30179</v>
+      </c>
+      <c r="B1168">
+        <v>2025</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F1168" t="s">
+        <v>3015</v>
+      </c>
+      <c r="H1168" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1169">
+        <v>30184</v>
+      </c>
+      <c r="B1169">
+        <v>2025</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F1169" t="s">
+        <v>3016</v>
+      </c>
+      <c r="H1169" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1170">
+        <v>30187</v>
+      </c>
+      <c r="B1170">
+        <v>2025</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>3017</v>
+      </c>
+      <c r="H1170" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1171">
+        <v>30191</v>
+      </c>
+      <c r="B1171">
+        <v>2025</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>3018</v>
+      </c>
+      <c r="H1171" t="s">
+        <v>2986</v>
+      </c>
+      <c r="I1171" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1172">
+        <v>30192</v>
+      </c>
+      <c r="B1172">
+        <v>2025</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>3020</v>
+      </c>
+      <c r="H1172" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1173">
+        <v>30194</v>
+      </c>
+      <c r="B1173">
+        <v>2025</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>2984</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>3021</v>
+      </c>
+      <c r="H1173" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1174">
+        <v>30196</v>
+      </c>
+      <c r="B1174">
+        <v>2025</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>3022</v>
+      </c>
+      <c r="H1174" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1175">
+        <v>30198</v>
+      </c>
+      <c r="B1175">
+        <v>2025</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H1175" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1176">
+        <v>30205</v>
+      </c>
+      <c r="B1176">
+        <v>2025</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>3024</v>
+      </c>
+      <c r="H1176" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1177">
+        <v>30208</v>
+      </c>
+      <c r="B1177">
+        <v>2025</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H1177" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1178">
+        <v>30210</v>
+      </c>
+      <c r="B1178">
+        <v>2025</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>3026</v>
+      </c>
+      <c r="H1178" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1179">
+        <v>30003</v>
+      </c>
+      <c r="B1179">
+        <v>2025</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>3030</v>
+      </c>
+      <c r="H1179" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1179" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1180">
+        <v>30005</v>
+      </c>
+      <c r="B1180">
+        <v>2025</v>
+      </c>
+      <c r="E1180" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>3032</v>
+      </c>
+      <c r="H1180" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1180" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1181">
+        <v>30007</v>
+      </c>
+      <c r="B1181">
+        <v>2025</v>
+      </c>
+      <c r="E1181" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>3033</v>
+      </c>
+      <c r="H1181" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1181" t="s">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1182">
+        <v>30009</v>
+      </c>
+      <c r="B1182">
+        <v>2025</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>3034</v>
+      </c>
+      <c r="H1182" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1182" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1183">
+        <v>30011</v>
+      </c>
+      <c r="B1183">
+        <v>2025</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>3035</v>
+      </c>
+      <c r="H1183" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1183" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1184">
+        <v>30012</v>
+      </c>
+      <c r="B1184">
+        <v>2025</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>3036</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>3037</v>
+      </c>
+      <c r="H1184" s="3" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1184" t="s">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1185">
+        <v>30012</v>
+      </c>
+      <c r="B1185">
+        <v>2022</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>3113</v>
+      </c>
+      <c r="H1185" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1186">
+        <v>30014</v>
+      </c>
+      <c r="B1186">
+        <v>2025</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>3038</v>
+      </c>
+      <c r="H1186" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1186" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1187">
+        <v>30019</v>
+      </c>
+      <c r="B1187">
+        <v>2025</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>3039</v>
+      </c>
+      <c r="H1187" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1187" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1188">
+        <v>30026</v>
+      </c>
+      <c r="B1188">
+        <v>2025</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>3040</v>
+      </c>
+      <c r="H1188" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1188" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1189">
+        <v>30029</v>
+      </c>
+      <c r="B1189">
+        <v>2025</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>3041</v>
+      </c>
+      <c r="H1189" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1189" t="s">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1190">
+        <v>30030</v>
+      </c>
+      <c r="B1190">
+        <v>2025</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>3042</v>
+      </c>
+      <c r="H1190" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1190" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1191">
+        <v>30038</v>
+      </c>
+      <c r="B1191">
+        <v>2025</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>3043</v>
+      </c>
+      <c r="H1191" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1191" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1192">
+        <v>30039</v>
+      </c>
+      <c r="B1192">
+        <v>2025</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1192" t="s">
+        <v>3044</v>
+      </c>
+      <c r="H1192" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1192" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1193">
+        <v>30040</v>
+      </c>
+      <c r="B1193">
+        <v>2025</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1193" t="s">
+        <v>606</v>
+      </c>
+      <c r="H1193" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1193" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1194">
+        <v>30041</v>
+      </c>
+      <c r="B1194">
+        <v>2025</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1194" t="s">
+        <v>3045</v>
+      </c>
+      <c r="H1194" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1194" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1195">
+        <v>30044</v>
+      </c>
+      <c r="B1195">
+        <v>2025</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>3046</v>
+      </c>
+      <c r="H1195" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1195" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1196">
+        <v>30048</v>
+      </c>
+      <c r="B1196">
+        <v>2025</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>721</v>
+      </c>
+      <c r="H1196" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1196" t="s">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1197">
+        <v>30054</v>
+      </c>
+      <c r="B1197">
+        <v>2025</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>3047</v>
+      </c>
+      <c r="H1197" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1197" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1198">
+        <v>30057</v>
+      </c>
+      <c r="B1198">
+        <v>2025</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>3048</v>
+      </c>
+      <c r="H1198" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1198" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1199">
+        <v>30058</v>
+      </c>
+      <c r="B1199">
+        <v>2025</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>3049</v>
+      </c>
+      <c r="H1199" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1199" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1200">
+        <v>30059</v>
+      </c>
+      <c r="B1200">
+        <v>2025</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H1200" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1200" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1201">
+        <v>30061</v>
+      </c>
+      <c r="B1201">
+        <v>2025</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>3051</v>
+      </c>
+      <c r="H1201" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1201" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1202">
+        <v>30065</v>
+      </c>
+      <c r="B1202">
+        <v>2025</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>3052</v>
+      </c>
+      <c r="H1202" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1202" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1203">
+        <v>30068</v>
+      </c>
+      <c r="B1203">
+        <v>2025</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>3053</v>
+      </c>
+      <c r="H1203" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1203" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1204">
+        <v>30069</v>
+      </c>
+      <c r="B1204">
+        <v>2025</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>3054</v>
+      </c>
+      <c r="H1204" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1204" t="s">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1205">
+        <v>30071</v>
+      </c>
+      <c r="B1205">
+        <v>2025</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>3055</v>
+      </c>
+      <c r="H1205" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1206">
+        <v>30072</v>
+      </c>
+      <c r="B1206">
+        <v>2025</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>3056</v>
+      </c>
+      <c r="H1206" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1207">
+        <v>30073</v>
+      </c>
+      <c r="B1207">
+        <v>2025</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>3057</v>
+      </c>
+      <c r="H1207" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1208">
+        <v>30074</v>
+      </c>
+      <c r="B1208">
+        <v>2025</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>3058</v>
+      </c>
+      <c r="H1208" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1208" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1209">
+        <v>30080</v>
+      </c>
+      <c r="B1209">
+        <v>2025</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>3059</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1209" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1210">
+        <v>30081</v>
+      </c>
+      <c r="B1210">
+        <v>2025</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>3060</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1210" t="s">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1211">
+        <v>30082</v>
+      </c>
+      <c r="B1211">
+        <v>2025</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>3061</v>
+      </c>
+      <c r="H1211" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1211" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1212">
+        <v>30086</v>
+      </c>
+      <c r="B1212">
+        <v>2025</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H1212" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1213">
+        <v>30087</v>
+      </c>
+      <c r="B1213">
+        <v>2025</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H1213" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1214">
+        <v>30089</v>
+      </c>
+      <c r="B1214">
+        <v>2025</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>3062</v>
+      </c>
+      <c r="H1214" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1214" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1215">
+        <v>30092</v>
+      </c>
+      <c r="B1215">
+        <v>2025</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>3063</v>
+      </c>
+      <c r="H1215" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1215" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1216">
+        <v>30095</v>
+      </c>
+      <c r="B1216">
+        <v>2025</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>3064</v>
+      </c>
+      <c r="H1216" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1216" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1217">
+        <v>30101</v>
+      </c>
+      <c r="B1217">
+        <v>2025</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>3065</v>
+      </c>
+      <c r="H1217" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1217" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1218">
+        <v>30102</v>
+      </c>
+      <c r="B1218">
+        <v>2025</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>3066</v>
+      </c>
+      <c r="H1218" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1218" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1219">
+        <v>30104</v>
+      </c>
+      <c r="B1219">
+        <v>2025</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>3067</v>
+      </c>
+      <c r="H1219" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1219" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1220">
+        <v>30105</v>
+      </c>
+      <c r="B1220">
+        <v>2025</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>3068</v>
+      </c>
+      <c r="H1220" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1221">
+        <v>30108</v>
+      </c>
+      <c r="B1221">
+        <v>2025</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H1221" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1222">
+        <v>30109</v>
+      </c>
+      <c r="B1222">
+        <v>2025</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H1222" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1222" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1223">
+        <v>30110</v>
+      </c>
+      <c r="B1223">
+        <v>2025</v>
+      </c>
+      <c r="E1223" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>3070</v>
+      </c>
+      <c r="H1223" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1224">
+        <v>30112</v>
+      </c>
+      <c r="B1224">
+        <v>2025</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>3071</v>
+      </c>
+      <c r="H1224" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1225">
+        <v>30113</v>
+      </c>
+      <c r="B1225">
+        <v>2025</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>3072</v>
+      </c>
+      <c r="H1225" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1225" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1226">
+        <v>30115</v>
+      </c>
+      <c r="B1226">
+        <v>2025</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>3073</v>
+      </c>
+      <c r="H1226" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1227">
+        <v>30118</v>
+      </c>
+      <c r="B1227">
+        <v>2025</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H1227" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1228">
+        <v>30119</v>
+      </c>
+      <c r="B1228">
+        <v>2025</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>3074</v>
+      </c>
+      <c r="H1228" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1229">
+        <v>30123</v>
+      </c>
+      <c r="B1229">
+        <v>2025</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>3075</v>
+      </c>
+      <c r="H1229" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1230">
+        <v>30124</v>
+      </c>
+      <c r="B1230">
+        <v>2025</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>3076</v>
+      </c>
+      <c r="H1230" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1231">
+        <v>30125</v>
+      </c>
+      <c r="B1231">
+        <v>2025</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>3077</v>
+      </c>
+      <c r="H1231" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1232">
+        <v>30126</v>
+      </c>
+      <c r="B1232">
+        <v>2025</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>3078</v>
+      </c>
+      <c r="H1232" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1233">
+        <v>30128</v>
+      </c>
+      <c r="B1233">
+        <v>2025</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>3079</v>
+      </c>
+      <c r="H1233" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1234">
+        <v>30129</v>
+      </c>
+      <c r="B1234">
+        <v>2025</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>3080</v>
+      </c>
+      <c r="H1234" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1234" t="s">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1235">
+        <v>30130</v>
+      </c>
+      <c r="B1235">
+        <v>2025</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>3081</v>
+      </c>
+      <c r="H1235" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1235" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1236">
+        <v>30131</v>
+      </c>
+      <c r="B1236">
+        <v>2025</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>3082</v>
+      </c>
+      <c r="H1236" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1236" t="s">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1237">
+        <v>30133</v>
+      </c>
+      <c r="B1237">
+        <v>2025</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>3083</v>
+      </c>
+      <c r="H1237" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1237" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1238">
+        <v>30134</v>
+      </c>
+      <c r="B1238">
+        <v>2025</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>3084</v>
+      </c>
+      <c r="H1238" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1238" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1239">
+        <v>30138</v>
+      </c>
+      <c r="B1239">
+        <v>2025</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>3085</v>
+      </c>
+      <c r="H1239" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1239" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1240">
+        <v>30141</v>
+      </c>
+      <c r="B1240">
+        <v>2025</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>3086</v>
+      </c>
+      <c r="H1240" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1240" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1241">
+        <v>30142</v>
+      </c>
+      <c r="B1241">
+        <v>2025</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>3087</v>
+      </c>
+      <c r="H1241" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1242">
+        <v>30143</v>
+      </c>
+      <c r="B1242">
+        <v>2025</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>3088</v>
+      </c>
+      <c r="H1242" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1242" t="s">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1243">
+        <v>30145</v>
+      </c>
+      <c r="B1243">
+        <v>2025</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>2021</v>
+      </c>
+      <c r="H1243" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1243" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1244">
+        <v>30146</v>
+      </c>
+      <c r="B1244">
+        <v>2025</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H1244" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1244" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1245">
+        <v>30148</v>
+      </c>
+      <c r="B1245">
+        <v>2025</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>3090</v>
+      </c>
+      <c r="H1245" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1245" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1246">
+        <v>30149</v>
+      </c>
+      <c r="B1246">
+        <v>2025</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>3091</v>
+      </c>
+      <c r="H1246" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1246" t="s">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1247">
+        <v>30154</v>
+      </c>
+      <c r="B1247">
+        <v>2025</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>3092</v>
+      </c>
+      <c r="H1247" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1247" t="s">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1248">
+        <v>30156</v>
+      </c>
+      <c r="B1248">
+        <v>2025</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>3093</v>
+      </c>
+      <c r="H1248" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1248" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1249">
+        <v>30158</v>
+      </c>
+      <c r="B1249">
+        <v>2025</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>3094</v>
+      </c>
+      <c r="H1249" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1249" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1250">
+        <v>30160</v>
+      </c>
+      <c r="B1250">
+        <v>2025</v>
+      </c>
+      <c r="E1250" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>3095</v>
+      </c>
+      <c r="H1250" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1251">
+        <v>30166</v>
+      </c>
+      <c r="B1251">
+        <v>2025</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>3096</v>
+      </c>
+      <c r="H1251" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1251" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1252">
+        <v>30168</v>
+      </c>
+      <c r="B1252">
+        <v>2025</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>2339</v>
+      </c>
+      <c r="H1252" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1252" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1253">
+        <v>30169</v>
+      </c>
+      <c r="B1253">
+        <v>2025</v>
+      </c>
+      <c r="E1253" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>3097</v>
+      </c>
+      <c r="H1253" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1254">
+        <v>30171</v>
+      </c>
+      <c r="B1254">
+        <v>2025</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>3098</v>
+      </c>
+      <c r="H1254" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1254" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1255">
+        <v>30174</v>
+      </c>
+      <c r="B1255">
+        <v>2025</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>3099</v>
+      </c>
+      <c r="H1255" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1255" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1256">
+        <v>30175</v>
+      </c>
+      <c r="B1256">
+        <v>2025</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>2426</v>
+      </c>
+      <c r="H1256" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1256" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1257">
+        <v>30180</v>
+      </c>
+      <c r="B1257">
+        <v>2025</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>3100</v>
+      </c>
+      <c r="H1257" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1257" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1258">
+        <v>30183</v>
+      </c>
+      <c r="B1258">
+        <v>2025</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>3101</v>
+      </c>
+      <c r="H1258" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1258" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1259">
+        <v>30188</v>
+      </c>
+      <c r="B1259">
+        <v>2025</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>3102</v>
+      </c>
+      <c r="H1259" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1259" t="s">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1260">
+        <v>30190</v>
+      </c>
+      <c r="B1260">
+        <v>2025</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>3103</v>
+      </c>
+      <c r="H1260" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>3142</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1261">
+        <v>30193</v>
+      </c>
+      <c r="B1261">
+        <v>2025</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>3104</v>
+      </c>
+      <c r="H1261" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1261" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1262">
+        <v>30201</v>
+      </c>
+      <c r="B1262">
+        <v>2025</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>3105</v>
+      </c>
+      <c r="H1262" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1262" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1263">
+        <v>30203</v>
+      </c>
+      <c r="B1263">
+        <v>2025</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1264">
+        <v>30204</v>
+      </c>
+      <c r="B1264">
+        <v>2025</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>3107</v>
+      </c>
+      <c r="H1264" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I1264" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1265">
+        <v>30206</v>
+      </c>
+      <c r="B1265">
+        <v>2025</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>3108</v>
+      </c>
+      <c r="H1265" s="2" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1266">
+        <v>30211</v>
+      </c>
+      <c r="B1266">
+        <v>2025</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>2935</v>
+      </c>
+      <c r="H1266" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1266" t="s">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1267">
+        <v>30212</v>
+      </c>
+      <c r="B1267">
+        <v>2025</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>3109</v>
+      </c>
+      <c r="H1267" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1267" t="s">
+        <v>3145</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S1106" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="6">
